--- a/DataAnalysis/CJ/0.3/Results.xlsx
+++ b/DataAnalysis/CJ/0.3/Results.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Utente\Desktop\CultureAwarenessTest\DataAnalysis\CJ\0.3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{079BCABB-6426-4570-BDE5-5D615C723E58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{690F2870-6295-4D2B-B9F4-D79B1D8033B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -422,143 +422,143 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B1:N4"/>
+  <dimension ref="A1:K4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1" t="s">
+        <v>7</v>
+      </c>
       <c r="E1" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G1" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="H1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I1" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="J1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K1" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1" t="s">
-        <v>13</v>
-      </c>
-      <c r="M1" t="s">
-        <v>14</v>
-      </c>
-      <c r="N1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B2" t="s">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
         <v>16</v>
       </c>
+      <c r="B2">
+        <v>20.9</v>
+      </c>
+      <c r="C2">
+        <v>2.9702225879927218</v>
+      </c>
+      <c r="D2">
+        <v>12.8</v>
+      </c>
       <c r="E2">
-        <v>20.9</v>
+        <v>1.9321835661585891</v>
       </c>
       <c r="F2">
-        <v>2.9702225879927218</v>
+        <v>30.8</v>
       </c>
       <c r="G2">
-        <v>12.8</v>
+        <v>1.6532795690182991</v>
       </c>
       <c r="H2">
-        <v>1.9321835661585891</v>
+        <v>21.499999999999996</v>
       </c>
       <c r="I2">
-        <v>30.8</v>
+        <v>1.0452715401237105</v>
       </c>
       <c r="J2">
-        <v>1.6532795690182991</v>
+        <v>8.6999999999999993</v>
       </c>
       <c r="K2">
-        <v>21.499999999999996</v>
-      </c>
-      <c r="L2">
-        <v>1.0452715401237105</v>
-      </c>
-      <c r="M2">
-        <v>8.6999999999999993</v>
-      </c>
-      <c r="N2">
         <v>1.6588706555520989</v>
       </c>
     </row>
-    <row r="3" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B3" t="s">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
         <v>20</v>
       </c>
+      <c r="B3">
+        <v>20.2</v>
+      </c>
+      <c r="C3">
+        <v>2.8416544476765622</v>
+      </c>
+      <c r="D3">
+        <v>14.1</v>
+      </c>
       <c r="E3">
-        <v>20.2</v>
+        <v>3.1304951684997073</v>
       </c>
       <c r="F3">
-        <v>2.8416544476765622</v>
+        <v>31.4</v>
       </c>
       <c r="G3">
-        <v>14.1</v>
+        <v>3.7815340802378015</v>
       </c>
       <c r="H3">
-        <v>3.1304951684997073</v>
+        <v>21.900000000000002</v>
       </c>
       <c r="I3">
-        <v>31.4</v>
+        <v>0.82158383625774856</v>
       </c>
       <c r="J3">
-        <v>3.7815340802378015</v>
+        <v>7.8</v>
       </c>
       <c r="K3">
-        <v>21.900000000000002</v>
-      </c>
-      <c r="L3">
-        <v>0.82158383625774856</v>
-      </c>
-      <c r="M3">
-        <v>7.8</v>
-      </c>
-      <c r="N3">
         <v>2.9425046020921268</v>
       </c>
     </row>
-    <row r="4" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B4" t="s">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
         <v>21</v>
       </c>
+      <c r="B4">
+        <v>20.8</v>
+      </c>
+      <c r="C4">
+        <v>0.75828754440515511</v>
+      </c>
+      <c r="D4">
+        <v>13.4</v>
+      </c>
       <c r="E4">
-        <v>20.8</v>
+        <v>0.65192024052026487</v>
       </c>
       <c r="F4">
-        <v>0.75828754440515511</v>
+        <v>31.9</v>
       </c>
       <c r="G4">
-        <v>13.4</v>
+        <v>3.4532593299664014</v>
       </c>
       <c r="H4">
-        <v>0.65192024052026487</v>
+        <v>22.033333333333335</v>
       </c>
       <c r="I4">
-        <v>31.9</v>
+        <v>1.31444961020869</v>
       </c>
       <c r="J4">
-        <v>3.4532593299664014</v>
+        <v>8.6333333333333346</v>
       </c>
       <c r="K4">
-        <v>22.033333333333335</v>
-      </c>
-      <c r="L4">
-        <v>1.31444961020869</v>
-      </c>
-      <c r="M4">
-        <v>8.6333333333333346</v>
-      </c>
-      <c r="N4">
         <v>1.4643921757659104</v>
       </c>
     </row>
